--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedProcedure</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedProcedure</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1141,7 +1141,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1201,7 +1201,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -1401,7 +1401,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
 </t>
   </si>
   <si>
@@ -2075,7 +2075,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.4140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.1171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1125,6 +1125,76 @@
     <t>PR1-6</t>
   </si>
   <si>
+    <t>Procedure.category.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe</t>
+  </si>
+  <si>
+    <t>MELGruppe</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.system</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/MOPED-LKFmedizinischeEinzelleistungen</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.version</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.code</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.display</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.category.text</t>
+  </si>
+  <si>
     <t>Procedure.code</t>
   </si>
   <si>
@@ -1132,7 +1202,7 @@
 </t>
   </si>
   <si>
-    <t>Identification of the procedure</t>
+    <t>Leistungskatalog BMSGPK</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -1141,7 +1211,10 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
+    <t>A code to identify a specific procedure .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1154,6 +1227,45 @@
   </si>
   <si>
     <t>PR1-3</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/ValueSet/moped-LKFLeistungskatalog-valueset</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/lkat-bmsgpk-2025</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.code.text</t>
   </si>
   <si>
     <t>Procedure.subject</t>
@@ -2047,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN70"/>
+  <dimension ref="A1:AN93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.45703125" customWidth="true" bestFit="true"/>
@@ -6440,11 +6552,11 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>87</v>
@@ -6456,21 +6568,19 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>163</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>361</v>
+        <v>164</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6494,11 +6604,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6516,7 +6628,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6525,41 +6637,41 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>167</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6568,18 +6680,20 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6616,51 +6730,51 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>375</v>
+        <v>167</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6671,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6683,16 +6797,20 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>378</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6728,25 +6846,23 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>377</v>
+        <v>205</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6758,29 +6874,31 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>87</v>
@@ -6795,18 +6913,20 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>382</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>202</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6830,13 +6950,11 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6854,13 +6972,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6869,24 +6987,24 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>206</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>389</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6894,7 +7012,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6906,20 +7024,18 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>89</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6968,7 +7084,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6977,41 +7093,41 @@
         <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>397</v>
+        <v>167</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>398</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7020,18 +7136,20 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>136</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7068,40 +7186,40 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>173</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7109,10 +7227,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7120,7 +7238,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -7135,16 +7253,20 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7153,7 +7275,7 @@
         <v>20</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>20</v>
@@ -7192,7 +7314,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7210,25 +7332,25 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7247,18 +7369,18 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>414</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7306,7 +7428,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7321,24 +7443,24 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>228</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7349,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7361,16 +7483,18 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>233</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7418,39 +7542,39 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>236</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>425</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>238</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7470,19 +7594,21 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>223</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7530,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7539,10 +7665,10 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7551,29 +7677,29 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7582,21 +7708,23 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7644,19 +7772,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7665,53 +7793,53 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>260</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>261</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7760,19 +7888,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>264</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7781,26 +7909,26 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7818,14 +7946,14 @@
         <v>186</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7853,10 +7981,10 @@
         <v>345</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7874,7 +8002,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7889,24 +8017,24 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>442</v>
+        <v>390</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>443</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7914,7 +8042,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
@@ -7926,21 +8054,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>445</v>
+        <v>89</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>163</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>164</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7988,50 +8114,50 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>444</v>
+        <v>165</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>449</v>
+        <v>166</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>453</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8043,20 +8169,18 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>455</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>170</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8092,31 +8216,31 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>454</v>
+        <v>173</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>449</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8125,7 +8249,7 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>460</v>
+        <v>167</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8133,10 +8257,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8147,7 +8271,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8156,19 +8280,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>289</v>
+        <v>200</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>201</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8192,13 +8320,11 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8216,13 +8342,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>461</v>
+        <v>205</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8237,18 +8363,18 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8268,16 +8394,16 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>465</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>466</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>467</v>
+        <v>164</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8328,7 +8454,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>464</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8337,34 +8463,34 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>468</v>
+        <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>469</v>
+        <v>167</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>470</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8380,19 +8506,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>472</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>474</v>
+        <v>170</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>475</v>
+        <v>138</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8418,31 +8544,31 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>476</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>477</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>173</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8454,27 +8580,27 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>480</v>
+        <v>167</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>481</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8485,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8497,18 +8623,20 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>483</v>
+        <v>214</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>484</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8517,7 +8645,7 @@
         <v>20</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>20</v>
@@ -8532,13 +8660,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>487</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8556,13 +8684,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>218</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8577,18 +8705,18 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>488</v>
+        <v>219</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>489</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8611,16 +8739,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>491</v>
+        <v>224</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>492</v>
+        <v>225</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>493</v>
+        <v>226</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8646,13 +8774,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>494</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>495</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8670,7 +8798,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>227</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8691,18 +8819,18 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>496</v>
+        <v>228</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8713,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8722,21 +8850,21 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>499</v>
+        <v>232</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8784,16 +8912,16 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
@@ -8805,18 +8933,18 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>502</v>
+        <v>238</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>503</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>503</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8827,7 +8955,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8836,21 +8964,21 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>504</v>
+        <v>223</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>242</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8874,13 +9002,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>508</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>509</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8898,16 +9026,16 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>503</v>
+        <v>245</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -8919,18 +9047,18 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>510</v>
+        <v>246</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>403</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>511</v>
+        <v>403</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8941,7 +9069,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8950,19 +9078,23 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>512</v>
+        <v>251</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8986,13 +9118,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>514</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9010,13 +9142,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>511</v>
+        <v>255</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -9031,18 +9163,18 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>516</v>
+        <v>256</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>517</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>517</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9053,7 +9185,7 @@
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9062,19 +9194,23 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>518</v>
+        <v>223</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>519</v>
+        <v>260</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9122,13 +9258,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>517</v>
+        <v>264</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9137,35 +9273,35 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>522</v>
+        <v>265</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>523</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9174,16 +9310,16 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>525</v>
+        <v>408</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>526</v>
+        <v>409</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9234,13 +9370,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9249,24 +9385,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>527</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>528</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9286,16 +9422,16 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>164</v>
+        <v>417</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9346,7 +9482,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9355,19 +9491,19 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9375,21 +9511,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>529</v>
+        <v>418</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>529</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9398,19 +9534,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>170</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>138</v>
+        <v>422</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9460,75 +9596,73 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>167</v>
+        <v>425</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>427</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -9576,39 +9710,39 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AG66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="AN66" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9628,16 +9762,16 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>186</v>
+        <v>437</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>532</v>
+        <v>438</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>533</v>
+        <v>439</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9664,13 +9798,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>535</v>
+        <v>20</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>536</v>
+        <v>20</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9688,7 +9822,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9703,13 +9837,13 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>537</v>
+        <v>442</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -9717,10 +9851,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9728,7 +9862,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>87</v>
@@ -9740,16 +9874,16 @@
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>539</v>
+        <v>444</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>540</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>541</v>
+        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9800,10 +9934,10 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>87</v>
@@ -9818,10 +9952,10 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -9829,21 +9963,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9852,22 +9986,20 @@
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>544</v>
+        <v>451</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>548</v>
+        <v>454</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9892,13 +10024,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>549</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9916,13 +10048,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
@@ -9931,13 +10063,13 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>551</v>
+        <v>457</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -9945,10 +10077,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9968,16 +10100,16 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>553</v>
+        <v>459</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>554</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10028,7 +10160,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10040,18 +10172,2628 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="M85" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1144,7 +1144,7 @@
     <t>MELGruppe</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
+    <t>https://elga.moped.at/ValueSet/LKFmedizinischeEinzelleistungen</t>
   </si>
   <si>
     <t>Procedure.category.coding:MELGruppe.id</t>
@@ -1165,7 +1165,7 @@
     <t>Procedure.category.coding.system</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-LKFmedizinischeEinzelleistungen</t>
+    <t>https://elga.moped.at/CodeSystem/LKFmedizinischeEinzelleistungenCS</t>
   </si>
   <si>
     <t>Procedure.category.coding:MELGruppe.version</t>
@@ -1238,7 +1238,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-LKFLeistungskatalog-valueset</t>
+    <t>https://elga.moped.at/ValueSet/LKFLeistungskatalog</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -2187,7 +2187,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.1171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
